--- a/CSI_KARE_ML_Pipeline_Participants_List.xlsx
+++ b/CSI_KARE_ML_Pipeline_Participants_List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Participants" sheetId="1" r:id="rId1"/>
+    <sheet name="Participants List" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F263"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -2455,7 +2455,7 @@
         <v>MANUKINDA KRISHNAVAMSI</v>
       </c>
       <c r="C103" t="str">
-        <v>999240040148</v>
+        <v>99240040148</v>
       </c>
       <c r="D103" t="str">
         <v>24S02</v>
@@ -5607,9 +5607,69 @@
         <v>CSE</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="str">
+        <v>DADIREDDI VARSHITHA</v>
+      </c>
+      <c r="C261" t="str">
+        <v>99240040687</v>
+      </c>
+      <c r="D261" t="str">
+        <v>24S08</v>
+      </c>
+      <c r="E261" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F261" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="str">
+        <v>V MALLIKARJUNA</v>
+      </c>
+      <c r="C262" t="str">
+        <v>99240040181</v>
+      </c>
+      <c r="D262" t="str">
+        <v>24S18</v>
+      </c>
+      <c r="E262" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F262" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="str">
+        <v>BOMMADI ISHANT SRI</v>
+      </c>
+      <c r="C263" t="str">
+        <v>99240040405</v>
+      </c>
+      <c r="D263" t="str">
+        <v>24S04</v>
+      </c>
+      <c r="E263" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F263" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F260"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/CSI_KARE_ML_Pipeline_Participants_List.xlsx
+++ b/CSI_KARE_ML_Pipeline_Participants_List.xlsx
@@ -397,15 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F263"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F280"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5667,9 +5659,349 @@
         <v>CSE</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="str">
+        <v>KUNCHAM LAKSHMI NARASIMHA REDDY</v>
+      </c>
+      <c r="C264" t="str">
+        <v>99230040631</v>
+      </c>
+      <c r="D264" t="str">
+        <v>S08</v>
+      </c>
+      <c r="E264" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F264" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="str">
+        <v>DADIYALA HITHESH</v>
+      </c>
+      <c r="C265" t="str">
+        <v>99230040905</v>
+      </c>
+      <c r="D265" t="str">
+        <v>S08</v>
+      </c>
+      <c r="E265" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F265" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="str">
+        <v>KANNA PRANAVI SRINIVAS</v>
+      </c>
+      <c r="C266" t="str">
+        <v>99230040932</v>
+      </c>
+      <c r="D266" t="str">
+        <v>S08</v>
+      </c>
+      <c r="E266" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F266" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="str">
+        <v>P. TEJA SIMHA REDDY</v>
+      </c>
+      <c r="C267" t="str">
+        <v>9923005316</v>
+      </c>
+      <c r="D267" t="str">
+        <v>ECE-A</v>
+      </c>
+      <c r="E267" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F267" t="str">
+        <v>ECE</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="str">
+        <v>K. GURU TEJA</v>
+      </c>
+      <c r="C268" t="str">
+        <v>9923005320</v>
+      </c>
+      <c r="D268" t="str">
+        <v>ECE-A</v>
+      </c>
+      <c r="E268" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F268" t="str">
+        <v>ECE</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="str">
+        <v>D. ANJANEYULU</v>
+      </c>
+      <c r="C269" t="str">
+        <v>9923005074</v>
+      </c>
+      <c r="D269" t="str">
+        <v>ECE-A</v>
+      </c>
+      <c r="E269" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F269" t="str">
+        <v>ECE</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="str">
+        <v>AYULURI SOMANADH MADHAVA REDDY</v>
+      </c>
+      <c r="C270" t="str">
+        <v>99230041030</v>
+      </c>
+      <c r="D270" t="str">
+        <v>23S13</v>
+      </c>
+      <c r="E270" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F270" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="str">
+        <v>G. HEMALATHA</v>
+      </c>
+      <c r="C271" t="str">
+        <v>99230040300</v>
+      </c>
+      <c r="D271" t="str">
+        <v>S04</v>
+      </c>
+      <c r="E271" t="str">
+        <v>IV Year</v>
+      </c>
+      <c r="F271" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="str">
+        <v>SHAIK MOHAMMED TAHEER</v>
+      </c>
+      <c r="C272" t="str">
+        <v>99240040767</v>
+      </c>
+      <c r="D272" t="str">
+        <v>24S09</v>
+      </c>
+      <c r="E272" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F272" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="str">
+        <v>SEELAM BHANU PRAKASH REDDY</v>
+      </c>
+      <c r="C273" t="str">
+        <v>99240040783</v>
+      </c>
+      <c r="D273" t="str">
+        <v>24S09</v>
+      </c>
+      <c r="E273" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F273" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="str">
+        <v>DEGA RAKESH</v>
+      </c>
+      <c r="C274" t="str">
+        <v>99240040777</v>
+      </c>
+      <c r="D274" t="str">
+        <v>24S09</v>
+      </c>
+      <c r="E274" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F274" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="str">
+        <v>DOKKA OMKAR</v>
+      </c>
+      <c r="C275" t="str">
+        <v>9924005238</v>
+      </c>
+      <c r="D275" t="str">
+        <v>ECE-A</v>
+      </c>
+      <c r="E275" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F275" t="str">
+        <v>ECE</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="str">
+        <v>MODDURU LALITHA</v>
+      </c>
+      <c r="C276" t="str">
+        <v>9924005108</v>
+      </c>
+      <c r="D276" t="str">
+        <v>F</v>
+      </c>
+      <c r="E276" t="str">
+        <v>III Year</v>
+      </c>
+      <c r="F276" t="str">
+        <v>ECE</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="str">
+        <v>KALLAMADI VENUMADHAV REDDY</v>
+      </c>
+      <c r="C277" t="str">
+        <v>99250040348</v>
+      </c>
+      <c r="D277" t="str">
+        <v>25S04</v>
+      </c>
+      <c r="E277" t="str">
+        <v>II Year</v>
+      </c>
+      <c r="F277" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" t="str">
+        <v>MACHA PUNEEETH RAM</v>
+      </c>
+      <c r="C278" t="str">
+        <v>99250040322</v>
+      </c>
+      <c r="D278" t="str">
+        <v>25S04</v>
+      </c>
+      <c r="E278" t="str">
+        <v>II Year</v>
+      </c>
+      <c r="F278" t="str">
+        <v>CSE</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="str">
+        <v>G. MANOJ</v>
+      </c>
+      <c r="C279" t="str">
+        <v>99250040229</v>
+      </c>
+      <c r="D279" t="str">
+        <v>25S03</v>
+      </c>
+      <c r="E279" t="str">
+        <v>II Year</v>
+      </c>
+      <c r="F279" t="str">
+        <v>CSE (AI &amp; ML)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="str">
+        <v>IRALA HEMANTH</v>
+      </c>
+      <c r="C280" t="str">
+        <v>99250040392</v>
+      </c>
+      <c r="D280" t="str">
+        <v>25S05</v>
+      </c>
+      <c r="E280" t="str">
+        <v>II Year</v>
+      </c>
+      <c r="F280" t="str">
+        <v>CSE (AI &amp; ML)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F280"/>
   </ignoredErrors>
 </worksheet>
 </file>